--- a/FrontEnd-Laboratory/FB_Section_Lab_Task_Marks/FB_SectionLab_Task_Marks.xlsx
+++ b/FrontEnd-Laboratory/FB_Section_Lab_Task_Marks/FB_SectionLab_Task_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdb18f69be515abb/Desktop/Front_End_Lab/FrontEnd-Laboratory/FB_Section_Lab_Task_Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3C358D2-8E5F-4229-B32F-3E15E3D2D741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C3C358D2-8E5F-4229-B32F-3E15E3D2D741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A77A403-0E64-40BF-9827-618AE331CF19}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3059C0D7-C06B-432F-B61C-DE3123D1CC9A}"/>
+    <workbookView minimized="1" xWindow="5748" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{3059C0D7-C06B-432F-B61C-DE3123D1CC9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Roolnumber</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>Task3</t>
+  </si>
+  <si>
+    <t>Task 4</t>
   </si>
 </sst>
 </file>
@@ -419,10 +422,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD82139-F099-4350-99E4-F9A2CD269473}">
-  <dimension ref="B2:E68"/>
+  <dimension ref="B2:F68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -435,8 +438,11 @@
       <c r="E2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" cm="1">
         <f t="array" ref="B3:B62">_xlfn.SEQUENCE(60)</f>
         <v>1</v>
@@ -448,7 +454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -459,7 +465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -470,7 +476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -480,8 +486,14 @@
       <c r="D6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>5</v>
       </c>
@@ -492,7 +504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -503,7 +515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>7</v>
       </c>
@@ -514,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>8</v>
       </c>
@@ -524,13 +536,19 @@
       <c r="D10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>10</v>
       </c>
@@ -541,7 +559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>11</v>
       </c>
@@ -552,7 +570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>12</v>
       </c>
@@ -563,7 +581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>13</v>
       </c>
@@ -574,12 +592,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>15</v>
       </c>
@@ -590,7 +608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>16</v>
       </c>
@@ -601,7 +619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>17</v>
       </c>
@@ -612,7 +630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>18</v>
       </c>
@@ -623,7 +641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>19</v>
       </c>
@@ -634,7 +652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>20</v>
       </c>
@@ -645,7 +663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>21</v>
       </c>
@@ -656,7 +674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>22</v>
       </c>
@@ -667,7 +685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>23</v>
       </c>
@@ -678,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>24</v>
       </c>
@@ -689,7 +707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>25</v>
       </c>
@@ -700,7 +718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>26</v>
       </c>
@@ -713,8 +731,11 @@
       <c r="E28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>27</v>
       </c>
@@ -724,8 +745,14 @@
       <c r="D29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>28</v>
       </c>
@@ -735,8 +762,14 @@
       <c r="D30">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>29</v>
       </c>
@@ -747,7 +780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>30</v>
       </c>
@@ -758,7 +791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>31</v>
       </c>
@@ -769,7 +802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>32</v>
       </c>
@@ -780,7 +813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>33</v>
       </c>
@@ -791,12 +824,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>35</v>
       </c>
@@ -807,12 +840,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>37</v>
       </c>
@@ -823,7 +856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>38</v>
       </c>
@@ -834,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>39</v>
       </c>
@@ -844,13 +877,19 @@
       <c r="D41">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>41</v>
       </c>
@@ -861,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>42</v>
       </c>
@@ -872,12 +911,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>44</v>
       </c>
@@ -888,7 +927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>45</v>
       </c>
@@ -899,12 +938,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>47</v>
       </c>
@@ -915,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>48</v>
       </c>
@@ -926,7 +965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>49</v>
       </c>
@@ -936,8 +975,11 @@
       <c r="D51">
         <v>6</v>
       </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>50</v>
       </c>
@@ -948,7 +990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>51</v>
       </c>
@@ -959,7 +1001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>52</v>
       </c>
@@ -970,7 +1012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>53</v>
       </c>
@@ -981,7 +1023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>54</v>
       </c>
@@ -992,7 +1034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>55</v>
       </c>
@@ -1002,8 +1044,14 @@
       <c r="D57">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>56</v>
       </c>
@@ -1014,7 +1062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>57</v>
       </c>
@@ -1025,7 +1073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>58</v>
       </c>
@@ -1036,7 +1084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>59</v>
       </c>
@@ -1047,7 +1095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>60</v>
       </c>
@@ -1058,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>61</v>
       </c>
@@ -1069,7 +1117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>62</v>
       </c>
